--- a/data/trans_orig/IP1022_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>89226</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99661</t>
+          <t>99674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104948</t>
+          <t>103729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130292</t>
+          <t>130201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196073</t>
+          <t>200206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227049</t>
+          <t>226946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88867</t>
+          <t>88215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94099</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>81819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91542</t>
+          <t>91764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173162</t>
+          <t>172293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184647</t>
+          <t>184594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52055</t>
+          <t>51793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>61401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101315</t>
+          <t>100549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111680</t>
+          <t>111419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178219</t>
+          <t>182877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209580</t>
+          <t>209992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194270</t>
+          <t>193937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206100</t>
+          <t>205955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383407</t>
+          <t>383269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412310</t>
+          <t>411697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>108076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116636</t>
+          <t>116658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144606</t>
+          <t>144963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156823</t>
+          <t>156555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256598</t>
+          <t>255904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271142</t>
+          <t>270571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55692</t>
+          <t>55693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>64655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>61460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70440</t>
+          <t>70451</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121094</t>
+          <t>121632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133713</t>
+          <t>133696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>64259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>43118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77298</t>
+          <t>76875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78679</t>
+          <t>80452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126078</t>
+          <t>126160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594983</t>
+          <t>592470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>624926</t>
+          <t>625608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>667692</t>
+          <t>668115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>701813</t>
+          <t>701872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275641</t>
+          <t>1275559</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1323040</t>
+          <t>1321267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1022_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33179</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41164</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>113729</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>107464</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>95662</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>89226</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>99674</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>122465</t>
+          <t>93827</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130201</t>
+          <t>97993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>218126</t>
+          <t>207557</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200206</t>
+          <t>199112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226946</t>
+          <t>213920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7691</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13849</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6466</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83707</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77549</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87550</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88215</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94093</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87710</t>
+          <t>94366</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81819</t>
+          <t>90847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91764</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>180272</t>
+          <t>178073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172293</t>
+          <t>171393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184594</t>
+          <t>182426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4851</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9618</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5417</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54998</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49643</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46444</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51205</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51793</t>
+          <t>47561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61401</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>107785</t>
+          <t>103382</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100549</t>
+          <t>98355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111419</t>
+          <t>106843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,62 +1749,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11979</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7622</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18670</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15950</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34525</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1862,67 +1862,67 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>185595</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178904</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>189952</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>201452</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>182877</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>209992</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>200990</t>
+          <t>166524</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193937</t>
+          <t>159573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205955</t>
+          <t>171403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>402442</t>
+          <t>352119</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383269</t>
+          <t>342317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411697</t>
+          <t>358128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217402</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217402</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217402</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>214036</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>214036</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>214036</t>
+          <t>178144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>431438</t>
+          <t>375718</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>431438</t>
+          <t>375718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>431438</t>
+          <t>375718</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5575</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16538</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6027</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2770</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11352</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137778</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>131705</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142668</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>113401</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>108076</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116658</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>151533</t>
+          <t>112416</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144963</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156555</t>
+          <t>115531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>264935</t>
+          <t>250194</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255904</t>
+          <t>242561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270571</t>
+          <t>256283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4206</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10883</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7951</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4240</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13202</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>64081</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>57404</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>66832</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>60944</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>55693</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>64655</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67534</t>
+          <t>62221</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61460</t>
+          <t>56325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>65839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>128478</t>
+          <t>126303</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121632</t>
+          <t>118534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133696</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48037</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37519</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>60576</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>43066</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31121</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>64259</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>56615</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43118</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76875</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>99681</t>
+          <t>87577</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80452</t>
+          <t>73207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126160</t>
+          <t>104790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>636981</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>624442</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>647499</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>872</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>613663</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>592470</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>625608</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>90,22%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>688375</t>
+          <t>580647</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>668115</t>
+          <t>568947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>701872</t>
+          <t>589204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1302038</t>
+          <t>1217628</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275559</t>
+          <t>1200415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321267</t>
+          <t>1231998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>685018</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>685018</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685018</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>656729</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>656729</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>656729</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>744990</t>
+          <t>620187</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>744990</t>
+          <t>620187</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>744990</t>
+          <t>620187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1401719</t>
+          <t>1305205</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1401719</t>
+          <t>1305205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1401719</t>
+          <t>1305205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
